--- a/data/trans_orig/IP24_R2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R2_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43148</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36562</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49166</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50425</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43369</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>58159</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>68,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47503</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>40471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105407</t>
+          <t>78060</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116003</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20997</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14979</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27583</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22857</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15123</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29913</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31,19%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>16010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31863</t>
+          <t>26836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47241</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58552</t>
+          <t>51416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14538</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8919</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22589</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>45062</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20119</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>83955</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>66,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t>25470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122329</t>
+          <t>46299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>98981</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>90930</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>104600</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>81397</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42504</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>106340</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>64,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108105</t>
+          <t>79893</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99662</t>
+          <t>70170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114207</t>
+          <t>85977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>189502</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128779</t>
+          <t>167444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>215657</t>
+          <t>188273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>88,08%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9832</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3635</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11230</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53465</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49545</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56214</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>94,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>51503</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47038</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54633</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59907</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55595</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63133</t>
+          <t>53356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111409</t>
+          <t>103867</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105419</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116110</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15043</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5568</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35969</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9987</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5597</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15428</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>24924</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>46895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>32,79%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57119</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36193</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66594</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>60156</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54715</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>64546</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>60962</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>55568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71502</t>
+          <t>65450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>120448</t>
+          <t>118081</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85557</t>
+          <t>96110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132026</t>
+          <t>127909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3325</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38713</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36254</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39968</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37875</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>93,01%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74481</t>
+          <t>74321</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8344</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7840</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>4701</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12170</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>26,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>40598</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>36673</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43612</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>82,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>74,93%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>38327</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>33997</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>41466</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>83,02%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>73,64%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>89,82%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>38999</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40405</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>83884</t>
+          <t>79597</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77365</t>
+          <t>74292</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88674</t>
+          <t>84077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15391</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9625</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22837</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>21071</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>14678</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>29808</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26942</t>
+          <t>27191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>45838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>124692</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>117246</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>130458</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>89,01%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>102306</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>93569</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>108699</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>82,92%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>88,1%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>139111</t>
+          <t>101399</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131445</t>
+          <t>93822</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144488</t>
+          <t>107223</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>241418</t>
+          <t>226092</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>229209</t>
+          <t>215789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>251120</t>
+          <t>234436</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12103</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6922</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>18912</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>14244</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9436</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>20758</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>35011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>147318</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>140509</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>152499</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>92,41%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>117375</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>110861</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>122183</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>84,23%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>144871</t>
+          <t>126604</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138298</t>
+          <t>119718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149504</t>
+          <t>131637</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>262245</t>
+          <t>273922</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>254121</t>
+          <t>264907</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>269513</t>
+          <t>280947</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>124635</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>229313</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128550</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>251372</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>362673</t>
+          <t>256861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>508434</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>434516</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>539194</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>515435</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498972</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>530485</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1130630</t>
+          <t>1097319</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1058853</t>
+          <t>1067889</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1170154</t>
+          <t>1120398</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
